--- a/Database for udviklere/Lektion 3/mobilityticketing-lecture-3-starter-main/mobilityticketing-lecture-3-starter-main/docs/Responsibility matrix.xlsx
+++ b/Database for udviklere/Lektion 3/mobilityticketing-lecture-3-starter-main/mobilityticketing-lecture-3-starter-main/docs/Responsibility matrix.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nichlas\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nichlas\Documents\GitHub\Bachelor-opgaver\Database for udviklere\Lektion 3\mobilityticketing-lecture-3-starter-main\mobilityticketing-lecture-3-starter-main\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7E880283-3D47-463E-B932-96C65BEE28FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{716D9A5F-E482-4CD0-A718-3C0A4D915E99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25800" yWindow="0" windowWidth="25800" windowHeight="21000" xr2:uid="{2B16C1E5-592B-48A4-80CD-B2C53CF7C0C9}"/>
+    <workbookView xWindow="22845" yWindow="1830" windowWidth="21210" windowHeight="15435" xr2:uid="{2B16C1E5-592B-48A4-80CD-B2C53CF7C0C9}"/>
   </bookViews>
   <sheets>
     <sheet name="Ark1" sheetId="1" r:id="rId1"/>
@@ -541,7 +541,7 @@
         <v>13</v>
       </c>
       <c r="D5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E5" t="s">
         <v>12</v>
@@ -589,10 +589,10 @@
         <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E8" t="s">
         <v>11</v>
